--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N4"/>
+  <dimension ref="A1:N5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -534,12 +534,12 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>Tobias Foss</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Florian Lipowitz</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>Tobias Foss</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -574,7 +574,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Tadej Pogačar</t>
+          <t>Tadej Pogacar</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -599,17 +599,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>Romain Grégoire</t>
+          <t>Romain Gregoire</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>Lenny Martinez</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>Paul Seixas</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -695,6 +695,76 @@
       <c r="N4" t="inlineStr">
         <is>
           <t>Ilan Van Wilder</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-07-07</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Quinn Simmons</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Raul Garcia Pierna</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Marco Frigo</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Ramses Debruyne</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Kevin Vauquelin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Sean Quinn</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Torstein Traeen</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Mathias Vacek</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Pablo Castrillo</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Michael Matthews</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Alexandre Delettre</t>
         </is>
       </c>
     </row>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N6"/>
+  <dimension ref="A1:AG7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -487,6 +487,101 @@
           <t>12th</t>
         </is>
       </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>GC #1</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>GC #2</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>GC #3</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>GC #4</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>GC #5</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>GC #6</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>GC #7</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>GC #8</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>GC #9</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>GC #10</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Points #1</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Points #2</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Points #3</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>Mountain #1</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>Mountain #2</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>Mountain #3</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>Youth #1</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>Youth #2</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>Youth #3</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -557,6 +652,25 @@
           <t>Romain Gregoire</t>
         </is>
       </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -627,6 +741,25 @@
           <t>Juan Ayuso</t>
         </is>
       </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -697,6 +830,25 @@
           <t>Ilan Van Wilder</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -767,6 +919,25 @@
           <t>Alexandre Delettre</t>
         </is>
       </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -837,6 +1008,114 @@
           <t>Pascal Ackermann</t>
         </is>
       </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>2026-07-09</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>6</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Juan Ayuso</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Florian Lipowitz</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Mattias Skjelmose</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Lenny Martinez</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Sepp Kuss</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Egan Bernal</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>Jordan Jegat</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -629,39 +629,79 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>Florian Lipowitz</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>Tobias Foss</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Mathieu Van Der Poel</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Romain Gregoire</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Filippo Ganna</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Juan Ayuso</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Davide Piganzoli</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>Florian Lipowitz</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>Tobias Foss</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Paul Seixas</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Mathieu Van Der Poel</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>Romain Gregoire</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
       <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
@@ -741,25 +781,101 @@
           <t>Juan Ayuso</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
-      <c r="AE3" t="inlineStr"/>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="inlineStr"/>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>Mattias Skjelmose</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Tobias Halland Johannessen</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Romain Gregoire</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lenny Martinez</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Tom Pidcock</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -797,58 +913,134 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>Florian Lipowitz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>Lennert Van Eetvelt</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Juan Ayuso</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>Mattias Skjelmose</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Ilan Van Wilder</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Richard Carapaz</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>Tobias Halland Johannessen</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
         <is>
           <t>Florian Lipowitz</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Lennert Van Eetvelt</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>Remco Evenepoel</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>Isaac Del Toro</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="X4" t="inlineStr">
         <is>
           <t>Juan Ayuso</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Mattias Skjelmose</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>Ilan Van Wilder</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
-      <c r="AE4" t="inlineStr"/>
-      <c r="AF4" t="inlineStr"/>
-      <c r="AG4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Richard Carapaz</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>Richard Carapaz</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>Richard Carapaz</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -886,58 +1078,134 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
+          <t>Sean Quinn</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>Kevin Vauquelin</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Torstein Traeen</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Pablo Castrillo</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Mathias Vacek</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Michael Matthews</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Alexandre Delettre</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Quinn Simmons</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Raul Garcia Pierna</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Marco Frigo</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>Ramses Debruyne</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
         <is>
           <t>Sean Quinn</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kevin Vauquelin</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>Torstein Traeen</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Pablo Castrillo</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
         <is>
           <t>Mathias Vacek</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Pablo Castrillo</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Michael Matthews</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>Alexandre Delettre</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr"/>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
-      <c r="AE5" t="inlineStr"/>
-      <c r="AF5" t="inlineStr"/>
-      <c r="AG5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Quinn Simmons</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Raul Garcia Pierna</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Quinn Simmons</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>Raul Garcia Pierna</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>Quinn Simmons</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>Raul Garcia Pierna</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -975,58 +1243,134 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>Mads Pedersen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>Biniam Girmay</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Milan Fretin</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Anthony Turgis</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Soren Waerenskjold</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>Jenno Berckmoes</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>Pascal Ackermann</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>Olav Kooij</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Max Kanter</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Tim Merlier</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>Huub Artz</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>Jasper Philipsen</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
         <is>
           <t>Mads Pedersen</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Biniam Girmay</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
         <is>
           <t>Milan Fretin</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Anthony Turgis</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
         <is>
           <t>Soren Waerenskjold</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Anthony Turgis</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Jenno Berckmoes</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>Pascal Ackermann</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr"/>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
-      <c r="AE6" t="inlineStr"/>
-      <c r="AF6" t="inlineStr"/>
-      <c r="AG6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>Olav Kooij</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Max Kanter</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Tim Merlier</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>Olav Kooij</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Max Kanter</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>Tim Merlier</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>Olav Kooij</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>Max Kanter</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>Tim Merlier</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1097,25 +1441,101 @@
           <t>Jordan Jegat</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
-      <c r="AE7" t="inlineStr"/>
-      <c r="AF7" t="inlineStr"/>
-      <c r="AG7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>Remco Evenepoel</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>Paul Seixas</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Juan Ayuso</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Florian Lipowitz</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Mattias Skjelmose</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lenny Martinez</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Sepp Kuss</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>Tadej Pogacar</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>Jonas Vingegaard</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>Isaac Del Toro</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{27162AFD-6F46-4E5F-9CD7-74370A7CD890}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9BC922C-0254-4A15-9332-2A4D5BAC0E6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="162" uniqueCount="90">
   <si>
     <t>Date</t>
   </si>
@@ -275,6 +275,21 @@
   </si>
   <si>
     <t>Tadej Pogačar</t>
+  </si>
+  <si>
+    <t>2026-07-10</t>
+  </si>
+  <si>
+    <t>Phil Bauhaus</t>
+  </si>
+  <si>
+    <t>Dorian Godon</t>
+  </si>
+  <si>
+    <t>Tom Van Asbroeck</t>
+  </si>
+  <si>
+    <t>Pavel Bittner</t>
   </si>
 </sst>
 </file>
@@ -614,12 +629,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG7"/>
+  <dimension ref="A1:AG8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="5" max="6" width="17" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="26.28515625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
@@ -1069,6 +1085,107 @@
         <v>43</v>
       </c>
     </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>85</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>71</v>
+      </c>
+      <c r="D8" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" t="s">
+        <v>70</v>
+      </c>
+      <c r="G8" t="s">
+        <v>73</v>
+      </c>
+      <c r="H8" t="s">
+        <v>86</v>
+      </c>
+      <c r="I8" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" t="s">
+        <v>56</v>
+      </c>
+      <c r="K8" t="s">
+        <v>87</v>
+      </c>
+      <c r="L8" t="s">
+        <v>88</v>
+      </c>
+      <c r="M8" t="s">
+        <v>89</v>
+      </c>
+      <c r="N8" t="s">
+        <v>79</v>
+      </c>
+      <c r="O8" t="s">
+        <v>84</v>
+      </c>
+      <c r="P8" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>39</v>
+      </c>
+      <c r="R8" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" t="s">
+        <v>37</v>
+      </c>
+      <c r="T8" t="s">
+        <v>43</v>
+      </c>
+      <c r="U8" t="s">
+        <v>41</v>
+      </c>
+      <c r="V8" t="s">
+        <v>49</v>
+      </c>
+      <c r="W8" t="s">
+        <v>47</v>
+      </c>
+      <c r="X8" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y8" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z8" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA8" t="s">
+        <v>70</v>
+      </c>
+      <c r="AB8" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC8" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD8" t="s">
+        <v>49</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF8" t="s">
+        <v>37</v>
+      </c>
+      <c r="AG8" t="s">
+        <v>43</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0F7A2852-33EA-4A8D-B353-901C897700E6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E32572B7-0D08-4B3F-A925-60F84872FA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="226" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="95">
   <si>
     <t>Date</t>
   </si>
@@ -299,9 +312,6 @@
   </si>
   <si>
     <t>Clement Russo</t>
-  </si>
-  <si>
-    <t>2026-07-12</t>
   </si>
   <si>
     <t>Alex Baudin</t>
@@ -314,10 +324,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -343,8 +359,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,43 +664,39 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AG11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="24" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="9.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="12.88671875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="12.77734375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="15.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.6640625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="17" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="16.7109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -784,7 +797,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -828,7 +841,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -872,7 +885,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -916,7 +929,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -960,7 +973,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>68</v>
       </c>
@@ -1004,7 +1017,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -1105,7 +1118,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -1206,7 +1219,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -1307,9 +1320,9 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>93</v>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A10" s="1">
+        <v>46215</v>
       </c>
       <c r="B10">
         <v>9</v>
@@ -1324,7 +1337,7 @@
         <v>50</v>
       </c>
       <c r="F10" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G10" t="s">
         <v>35</v>
@@ -1339,7 +1352,7 @@
         <v>83</v>
       </c>
       <c r="K10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L10" t="s">
         <v>61</v>
@@ -1408,8 +1421,111 @@
         <v>43</v>
       </c>
     </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A11" s="1">
+        <v>46217</v>
+      </c>
+      <c r="B11">
+        <v>10</v>
+      </c>
+      <c r="C11" t="s">
+        <v>84</v>
+      </c>
+      <c r="D11" t="s">
+        <v>38</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
+        <v>41</v>
+      </c>
+      <c r="G11" t="s">
+        <v>37</v>
+      </c>
+      <c r="H11" t="s">
+        <v>47</v>
+      </c>
+      <c r="I11" t="s">
+        <v>34</v>
+      </c>
+      <c r="J11" t="s">
+        <v>39</v>
+      </c>
+      <c r="K11" t="s">
+        <v>50</v>
+      </c>
+      <c r="L11" t="s">
+        <v>49</v>
+      </c>
+      <c r="M11" t="s">
+        <v>53</v>
+      </c>
+      <c r="N11" t="s">
+        <v>40</v>
+      </c>
+      <c r="O11" t="s">
+        <v>84</v>
+      </c>
+      <c r="P11" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>38</v>
+      </c>
+      <c r="R11" t="s">
+        <v>37</v>
+      </c>
+      <c r="S11" t="s">
+        <v>43</v>
+      </c>
+      <c r="T11" t="s">
+        <v>41</v>
+      </c>
+      <c r="U11" t="s">
+        <v>39</v>
+      </c>
+      <c r="V11" t="s">
+        <v>47</v>
+      </c>
+      <c r="W11" t="s">
+        <v>49</v>
+      </c>
+      <c r="X11" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y11" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z11" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA11" t="s">
+        <v>71</v>
+      </c>
+      <c r="AB11" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC11" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD11" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG11" t="s">
+        <v>39</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E32572B7-0D08-4B3F-A925-60F84872FA8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E13E6B31-8947-42B7-992D-4CD2E2FD07D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="98">
   <si>
     <t>Date</t>
   </si>
@@ -318,6 +318,15 @@
   </si>
   <si>
     <t>Nicolas Breuillard</t>
+  </si>
+  <si>
+    <t>Søren Wærenskjold</t>
+  </si>
+  <si>
+    <t>Clément Russo</t>
+  </si>
+  <si>
+    <t>Fernando Gaviria</t>
   </si>
 </sst>
 </file>
@@ -664,7 +673,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG11"/>
+  <dimension ref="A1:AG13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -687,7 +696,8 @@
     <col min="22" max="23" width="17.42578125" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="13.85546875" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.42578125" bestFit="1" customWidth="1"/>
     <col min="28" max="28" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="29" max="29" width="16.42578125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
@@ -1521,6 +1531,110 @@
       <c r="AG11" t="s">
         <v>39</v>
       </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A12" s="1">
+        <v>46218</v>
+      </c>
+      <c r="B12">
+        <v>11</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
+      </c>
+      <c r="D12" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" t="s">
+        <v>74</v>
+      </c>
+      <c r="I12" t="s">
+        <v>76</v>
+      </c>
+      <c r="J12" t="s">
+        <v>96</v>
+      </c>
+      <c r="K12" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" t="s">
+        <v>79</v>
+      </c>
+      <c r="M12" t="s">
+        <v>56</v>
+      </c>
+      <c r="N12" t="s">
+        <v>91</v>
+      </c>
+      <c r="O12" t="s">
+        <v>84</v>
+      </c>
+      <c r="P12" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>38</v>
+      </c>
+      <c r="R12" t="s">
+        <v>37</v>
+      </c>
+      <c r="S12" t="s">
+        <v>43</v>
+      </c>
+      <c r="T12" t="s">
+        <v>41</v>
+      </c>
+      <c r="U12" t="s">
+        <v>39</v>
+      </c>
+      <c r="V12" t="s">
+        <v>47</v>
+      </c>
+      <c r="W12" t="s">
+        <v>49</v>
+      </c>
+      <c r="X12" t="s">
+        <v>50</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>74</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>37</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A13" s="1"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E13E6B31-8947-42B7-992D-4CD2E2FD07D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{417A1972-2E5A-4B61-BB53-38A98221AEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="98">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="287" uniqueCount="97">
   <si>
     <t>Date</t>
   </si>
@@ -318,9 +318,6 @@
   </si>
   <si>
     <t>Nicolas Breuillard</t>
-  </si>
-  <si>
-    <t>Søren Wærenskjold</t>
   </si>
   <si>
     <t>Clément Russo</t>
@@ -1540,7 +1537,7 @@
         <v>11</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="D12" t="s">
         <v>69</v>
@@ -1561,10 +1558,10 @@
         <v>76</v>
       </c>
       <c r="J12" t="s">
+        <v>95</v>
+      </c>
+      <c r="K12" t="s">
         <v>96</v>
-      </c>
-      <c r="K12" t="s">
-        <v>97</v>
       </c>
       <c r="L12" t="s">
         <v>79</v>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{417A1972-2E5A-4B61-BB53-38A98221AEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{417A1972-2E5A-4B61-BB53-38A98221AEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A239585-6AAD-4A25-8BB8-98ACF9870F3E}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1543,34 +1543,34 @@
         <v>69</v>
       </c>
       <c r="E12" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="F12" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="G12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="H12" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="I12" t="s">
-        <v>76</v>
+        <v>95</v>
       </c>
       <c r="J12" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K12" t="s">
-        <v>96</v>
+        <v>79</v>
       </c>
       <c r="L12" t="s">
-        <v>79</v>
+        <v>56</v>
       </c>
       <c r="M12" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="N12" t="s">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="O12" t="s">
         <v>84</v>
@@ -1609,7 +1609,7 @@
         <v>74</v>
       </c>
       <c r="AA12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="AB12" t="s">
         <v>84</v>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="8_{417A1972-2E5A-4B61-BB53-38A98221AEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A239585-6AAD-4A25-8BB8-98ACF9870F3E}"/>
+  <xr:revisionPtr revIDLastSave="10" documentId="8_{417A1972-2E5A-4B61-BB53-38A98221AEAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2FEAE150-6F19-4BE3-A25D-E648F88F5A0D}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1543,34 +1543,34 @@
         <v>69</v>
       </c>
       <c r="E12" t="s">
+        <v>73</v>
+      </c>
+      <c r="F12" t="s">
         <v>75</v>
       </c>
-      <c r="F12" t="s">
+      <c r="G12" t="s">
         <v>72</v>
       </c>
-      <c r="G12" t="s">
+      <c r="H12" t="s">
         <v>74</v>
       </c>
-      <c r="H12" t="s">
+      <c r="I12" t="s">
         <v>76</v>
       </c>
-      <c r="I12" t="s">
+      <c r="J12" t="s">
         <v>95</v>
       </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
         <v>96</v>
       </c>
-      <c r="K12" t="s">
+      <c r="L12" t="s">
         <v>79</v>
       </c>
-      <c r="L12" t="s">
+      <c r="M12" t="s">
         <v>56</v>
       </c>
-      <c r="M12" t="s">
+      <c r="N12" t="s">
         <v>91</v>
-      </c>
-      <c r="N12" t="s">
-        <v>78</v>
       </c>
       <c r="O12" t="s">
         <v>84</v>
@@ -1609,7 +1609,7 @@
         <v>74</v>
       </c>
       <c r="AA12" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="AB12" t="s">
         <v>84</v>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DPshonyak\OneDrive - BluCurrent Credit Union\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D0EA8F5-DCC8-449E-84E9-F998008B4CD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{AC361594-AE5C-4562-916B-086414334E5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="383" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="415" uniqueCount="113">
   <si>
     <t>Date</t>
   </si>
@@ -350,6 +350,15 @@
   </si>
   <si>
     <t>Valentin Paret-Peintre</t>
+  </si>
+  <si>
+    <t>Adam Yates</t>
+  </si>
+  <si>
+    <t>Yannis Voisard</t>
+  </si>
+  <si>
+    <t>2026-07-19</t>
   </si>
 </sst>
 </file>
@@ -359,10 +368,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -693,7 +708,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG15"/>
+  <dimension ref="A1:AG16"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
@@ -1956,7 +1971,109 @@
         <v>39</v>
       </c>
     </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>112</v>
+      </c>
+      <c r="B16">
+        <v>15</v>
+      </c>
+      <c r="C16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D16" t="s">
+        <v>84</v>
+      </c>
+      <c r="E16" t="s">
+        <v>39</v>
+      </c>
+      <c r="F16" t="s">
+        <v>43</v>
+      </c>
+      <c r="G16" t="s">
+        <v>41</v>
+      </c>
+      <c r="H16" t="s">
+        <v>49</v>
+      </c>
+      <c r="I16" t="s">
+        <v>47</v>
+      </c>
+      <c r="J16" t="s">
+        <v>37</v>
+      </c>
+      <c r="K16" t="s">
+        <v>110</v>
+      </c>
+      <c r="L16" t="s">
+        <v>57</v>
+      </c>
+      <c r="M16" t="s">
+        <v>111</v>
+      </c>
+      <c r="N16" t="s">
+        <v>53</v>
+      </c>
+      <c r="O16" t="s">
+        <v>84</v>
+      </c>
+      <c r="P16" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" t="s">
+        <v>43</v>
+      </c>
+      <c r="S16" t="s">
+        <v>41</v>
+      </c>
+      <c r="T16" t="s">
+        <v>37</v>
+      </c>
+      <c r="U16" t="s">
+        <v>47</v>
+      </c>
+      <c r="V16" t="s">
+        <v>49</v>
+      </c>
+      <c r="W16" t="s">
+        <v>50</v>
+      </c>
+      <c r="X16" t="s">
+        <v>83</v>
+      </c>
+      <c r="Y16" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA16" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB16" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC16" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD16" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE16" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97D1D9CA-7122-4913-BA04-B5669954AF79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4D79E5E-532C-4A5E-B2EA-8A7045F344F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Results" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="447" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="122">
   <si>
     <t>Date</t>
   </si>
@@ -374,6 +374,18 @@
   </si>
   <si>
     <t>Joshua Tarling</t>
+  </si>
+  <si>
+    <t>Lewis Askey</t>
+  </si>
+  <si>
+    <t>Aaron Gate</t>
+  </si>
+  <si>
+    <t>Hugo Page</t>
+  </si>
+  <si>
+    <t>2026-07-22</t>
   </si>
 </sst>
 </file>
@@ -383,10 +395,16 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -717,38 +735,38 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:AG18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="24" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.21875" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.88671875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.33203125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.88671875" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="15.88671875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.44140625" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.77734375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.44140625" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.21875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="13.85546875" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="15.85546875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="32" max="32" width="10" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.6640625" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -849,7 +867,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>33</v>
       </c>
@@ -893,7 +911,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>46</v>
       </c>
@@ -937,7 +955,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>52</v>
       </c>
@@ -981,7 +999,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>55</v>
       </c>
@@ -1025,7 +1043,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>68</v>
       </c>
@@ -1069,7 +1087,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>80</v>
       </c>
@@ -1170,7 +1188,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>85</v>
       </c>
@@ -1271,7 +1289,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>90</v>
       </c>
@@ -1372,7 +1390,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>93</v>
       </c>
@@ -1473,7 +1491,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>46217</v>
       </c>
@@ -1574,7 +1592,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="1">
         <v>46218</v>
       </c>
@@ -1675,7 +1693,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
         <v>46219</v>
       </c>
@@ -1776,7 +1794,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>99</v>
       </c>
@@ -1877,7 +1895,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>108</v>
       </c>
@@ -1978,7 +1996,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>110</v>
       </c>
@@ -2079,7 +2097,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>113</v>
       </c>
@@ -2180,7 +2198,109 @@
         <v>37</v>
       </c>
     </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>121</v>
+      </c>
+      <c r="B18">
+        <v>17</v>
+      </c>
+      <c r="C18" t="s">
+        <v>73</v>
+      </c>
+      <c r="D18" t="s">
+        <v>100</v>
+      </c>
+      <c r="E18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
+        <v>118</v>
+      </c>
+      <c r="G18" t="s">
+        <v>91</v>
+      </c>
+      <c r="H18" t="s">
+        <v>96</v>
+      </c>
+      <c r="I18" t="s">
+        <v>72</v>
+      </c>
+      <c r="J18" t="s">
+        <v>56</v>
+      </c>
+      <c r="K18" t="s">
+        <v>66</v>
+      </c>
+      <c r="L18" t="s">
+        <v>119</v>
+      </c>
+      <c r="M18" t="s">
+        <v>44</v>
+      </c>
+      <c r="N18" t="s">
+        <v>120</v>
+      </c>
+      <c r="O18" t="s">
+        <v>84</v>
+      </c>
+      <c r="P18" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>39</v>
+      </c>
+      <c r="R18" t="s">
+        <v>43</v>
+      </c>
+      <c r="S18" t="s">
+        <v>37</v>
+      </c>
+      <c r="T18" t="s">
+        <v>47</v>
+      </c>
+      <c r="U18" t="s">
+        <v>49</v>
+      </c>
+      <c r="V18" t="s">
+        <v>50</v>
+      </c>
+      <c r="W18" t="s">
+        <v>83</v>
+      </c>
+      <c r="X18" t="s">
+        <v>112</v>
+      </c>
+      <c r="Y18" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z18" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA18" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB18" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC18" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD18" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE18" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF18" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG18" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/tdf-results.xlsx
+++ b/tdf-results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://blucurrent-my.sharepoint.com/personal/dpshonyak_blucurrent_org/Documents/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4D79E5E-532C-4A5E-B2EA-8A7045F344F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9AF47E4-3AA5-444A-8C09-344AC03AEFD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-60" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="124">
   <si>
     <t>Date</t>
   </si>
@@ -376,6 +376,9 @@
     <t>Joshua Tarling</t>
   </si>
   <si>
+    <t>2026-07-22</t>
+  </si>
+  <si>
     <t>Lewis Askey</t>
   </si>
   <si>
@@ -385,7 +388,10 @@
     <t>Hugo Page</t>
   </si>
   <si>
-    <t>2026-07-22</t>
+    <t>2026-07-23</t>
+  </si>
+  <si>
+    <t>Matteo Jorgenson</t>
   </si>
 </sst>
 </file>
@@ -395,16 +401,10 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd\ h:mm:ss"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -735,35 +735,34 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG18"/>
+  <dimension ref="A1:AG19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="24" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="24" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="17.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.85546875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.28515625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="13.85546875" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="15.85546875" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="13.42578125" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="13.7109375" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="19.140625" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.7109375" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="10" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="19.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="26.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.5703125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="17" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="15.140625" bestFit="1" customWidth="1"/>
+    <col min="20" max="23" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="21.42578125" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="15" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="13.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.25">
@@ -2200,7 +2199,7 @@
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="B18">
         <v>17</v>
@@ -2215,7 +2214,7 @@
         <v>69</v>
       </c>
       <c r="F18" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="G18" t="s">
         <v>91</v>
@@ -2233,13 +2232,13 @@
         <v>66</v>
       </c>
       <c r="L18" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="M18" t="s">
         <v>44</v>
       </c>
       <c r="N18" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="O18" t="s">
         <v>84</v>
@@ -2299,8 +2298,108 @@
         <v>37</v>
       </c>
     </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>122</v>
+      </c>
+      <c r="B19">
+        <v>18</v>
+      </c>
+      <c r="C19" t="s">
+        <v>53</v>
+      </c>
+      <c r="D19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E19" t="s">
+        <v>123</v>
+      </c>
+      <c r="F19" t="s">
+        <v>109</v>
+      </c>
+      <c r="G19" t="s">
+        <v>48</v>
+      </c>
+      <c r="H19" t="s">
+        <v>64</v>
+      </c>
+      <c r="I19" t="s">
+        <v>58</v>
+      </c>
+      <c r="J19" t="s">
+        <v>49</v>
+      </c>
+      <c r="K19" t="s">
+        <v>38</v>
+      </c>
+      <c r="L19" t="s">
+        <v>50</v>
+      </c>
+      <c r="M19" t="s">
+        <v>83</v>
+      </c>
+      <c r="N19" t="s">
+        <v>37</v>
+      </c>
+      <c r="O19" t="s">
+        <v>84</v>
+      </c>
+      <c r="P19" t="s">
+        <v>38</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>39</v>
+      </c>
+      <c r="R19" t="s">
+        <v>43</v>
+      </c>
+      <c r="S19" t="s">
+        <v>37</v>
+      </c>
+      <c r="T19" t="s">
+        <v>47</v>
+      </c>
+      <c r="U19" t="s">
+        <v>49</v>
+      </c>
+      <c r="V19" t="s">
+        <v>50</v>
+      </c>
+      <c r="W19" t="s">
+        <v>83</v>
+      </c>
+      <c r="X19" t="s">
+        <v>53</v>
+      </c>
+      <c r="Y19" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z19" t="s">
+        <v>73</v>
+      </c>
+      <c r="AA19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AB19" t="s">
+        <v>84</v>
+      </c>
+      <c r="AC19" t="s">
+        <v>109</v>
+      </c>
+      <c r="AD19" t="s">
+        <v>53</v>
+      </c>
+      <c r="AE19" t="s">
+        <v>39</v>
+      </c>
+      <c r="AF19" t="s">
+        <v>43</v>
+      </c>
+      <c r="AG19" t="s">
+        <v>37</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
